--- a/Tecnical test/Data Files/KaryawanBaru_Data.xlsx
+++ b/Tecnical test/Data Files/KaryawanBaru_Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,10 +489,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -561,10 +559,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -629,10 +625,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -701,10 +695,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -773,10 +765,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
@@ -801,7 +791,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>kosong@sv.id</t>
+          <t>a5@sv.id</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -836,15 +826,13 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Nama wajib diisi</t>
+          <t>Nama Lengkap tidak boleh kosong!</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -869,7 +857,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ktp@sv.id</t>
+          <t>a6@sv.id</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -904,19 +892,17 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>KTP wajib diisi</t>
+          <t>Nomor KTP tidak boleh kosong!</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Test Email Salah</t>
+          <t>Test KTP Pendek</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -931,7 +917,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3201010101010007</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -941,7 +927,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>email@@salah</t>
+          <t>a7@sv.id</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -976,19 +962,17 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Format email tidak valid</t>
+          <t>Nomor KTP harus memiliki 16 digit!</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A9" t="n">
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Test HP Salah</t>
+          <t>Test Email Kosong</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1008,14 +992,10 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>abc123</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>hp@sv.id</t>
-        </is>
-      </c>
+          <t>081234567898</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>2026-08-15</t>
@@ -1048,19 +1028,17 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Format HP tidak valid</t>
+          <t>Email tidak boleh kosong!</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Test Tgl Depan</t>
+          <t>Test Email Salah</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1070,7 +1048,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>1995-05-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1085,7 +1063,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tgl@sv.id</t>
+          <t>email@@salah</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1120,19 +1098,17 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Tanggal lahir tidak valid</t>
+          <t>Format alamat email salah!</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A11" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Test Checkbox</t>
+          <t>Test Tgl Lahir Kosong</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1140,11 +1116,7 @@
           <t>Jakarta</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1995-05-10</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>3201010101010010</t>
@@ -1152,12 +1124,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>081234567800</t>
+          <t>081234567810</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>cb@sv.id</t>
+          <t>a10@sv.id</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1167,10 +1139,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Jl. Checkbox No.6</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>Jl. F No.6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Jl. F No.6</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>ktp10.jpg</t>
@@ -1183,24 +1159,22 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Domisili auto-fill</t>
+          <t>Tanggal Lahir tidak boleh kosong!</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A12" t="n">
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Test File Salah</t>
+          <t>Test File Non-Gambar</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1225,7 +1199,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>file@sv.id</t>
+          <t>a11@sv.id</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1235,12 +1209,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Jl. File No.7</t>
+          <t>Jl. G No.7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Jl. File No.7</t>
+          <t>Jl. G No.7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1260,19 +1234,17 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>File ditolak</t>
+          <t>error read ktp image file: EOF</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Test File Benar</t>
+          <t>Test Checkbox</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1292,12 +1264,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>081234567822</t>
+          <t>081234567812</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>filedu@sv.id</t>
+          <t>a12@sv.id</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1307,32 +1279,168 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Jl. File No.8</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Jl. File No.8</t>
-        </is>
-      </c>
+          <t>Jl. Checkbox No.6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
+          <t>ktp11.jpg</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>selfie12.jpg</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Test HP Non-Angka</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1995-05-10</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3201010101010013</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>abc123</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>a13@sv.id</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Jl. H No.8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Jl. H No.8</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>ktp12.jpg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>selfie12.jpg</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>File diterima</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Format nomor HP tidak valid</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Test Tgl Lahir Depan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2030-01-01</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3201010101010014</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>081234567814</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>a14@sv.id</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Jl. I No.9</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Jl. I No.9</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ktp1.jpg</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>selfie1.jpg</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Tanggal lahir tidak boleh di masa depan</t>
         </is>
       </c>
     </row>

--- a/Tecnical test/Data Files/KaryawanBaru_Data.xlsx
+++ b/Tecnical test/Data Files/KaryawanBaru_Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -602,7 +602,6 @@
           <t>Jl. Asia Afrika No.10 Bandung</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>ktp2.jpg</t>
@@ -768,7 +767,6 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Jakarta</t>
@@ -849,7 +847,6 @@
           <t>1995-05-10</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>081234567896</t>
@@ -995,7 +992,6 @@
           <t>081234567898</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>2026-08-15</t>
@@ -1116,7 +1112,6 @@
           <t>Jakarta</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>3201010101010010</t>
@@ -1235,212 +1230,6 @@
       <c r="N12" t="inlineStr">
         <is>
           <t>error read ktp image file: EOF</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Test Checkbox</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Jakarta</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1995-05-10</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>3201010101010012</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>081234567812</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>a12@sv.id</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Jl. Checkbox No.6</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>ktp11.jpg</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>selfie12.jpg</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Test HP Non-Angka</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Jakarta</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1995-05-10</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>3201010101010013</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>abc123</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>a13@sv.id</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Jl. H No.8</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Jl. H No.8</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>ktp12.jpg</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>selfie12.jpg</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Format nomor HP tidak valid</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Test Tgl Lahir Depan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Jakarta</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2030-01-01</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>3201010101010014</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>081234567814</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>a14@sv.id</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Jl. I No.9</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Jl. I No.9</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>ktp1.jpg</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>selfie1.jpg</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Tanggal lahir tidak boleh di masa depan</t>
         </is>
       </c>
     </row>

--- a/Tecnical test/Data Files/KaryawanBaru_Data.xlsx
+++ b/Tecnical test/Data Files/KaryawanBaru_Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1230,6 +1230,71 @@
       <c r="N12" t="inlineStr">
         <is>
           <t>error read ktp image file: EOF</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Test Checkbox</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1995-05-10</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3201010101010012</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>081234567812</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>a12@sv.id</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Jl. Checkbox No.6</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ktp11.jpg</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>selfie12.jpg</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Success</t>
         </is>
       </c>
     </row>
